--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -703,7 +703,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>728000</v>
+        <v>868000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1630,17 +1630,21 @@
     <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
-      </c>
-      <c r="B63" s="6"/>
+        <v>868000</v>
+      </c>
+      <c r="B63" s="6">
+        <v>140000</v>
+      </c>
       <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="D63" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -1650,7 +1654,7 @@
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1660,7 +1664,7 @@
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1670,7 +1674,7 @@
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1680,7 +1684,7 @@
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1690,7 +1694,7 @@
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1700,7 +1704,7 @@
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1711,7 +1715,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="7">
         <f>SUM(B52:B70)+B46</f>
-        <v>4146000</v>
+        <v>4286000</v>
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
@@ -1723,7 +1727,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>728000</v>
+        <v>868000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>وجه تکیه گول</t>
+  </si>
+  <si>
+    <t>1405/04/14</t>
   </si>
 </sst>
 </file>
@@ -703,7 +706,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1644,17 +1647,23 @@
     <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
-      </c>
-      <c r="B64" s="6"/>
+        <v>1085000</v>
+      </c>
+      <c r="B64" s="6">
+        <v>217000</v>
+      </c>
       <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="3"/>
+      <c r="D64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -1664,7 +1673,7 @@
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1674,7 +1683,7 @@
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1684,7 +1693,7 @@
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1694,7 +1703,7 @@
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1704,7 +1713,7 @@
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1715,7 +1724,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="7">
         <f>SUM(B52:B70)+B46</f>
-        <v>4286000</v>
+        <v>4503000</v>
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
@@ -1727,7 +1736,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>868000</v>
+        <v>1085000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>1405/04/14</t>
+  </si>
+  <si>
+    <t>1405/04/15</t>
+  </si>
+  <si>
+    <t>وج</t>
   </si>
 </sst>
 </file>
@@ -706,7 +712,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1663,17 +1669,23 @@
     <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="3"/>
+      <c r="C65" s="6">
+        <v>500000</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -1683,7 +1695,7 @@
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1693,7 +1705,7 @@
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1703,7 +1715,7 @@
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1713,7 +1725,7 @@
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1728,7 +1740,7 @@
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
-        <v>3418000</v>
+        <v>3918000</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
@@ -1736,7 +1748,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>1085000</v>
+        <v>585000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="78">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>وج</t>
+  </si>
+  <si>
+    <t>1405/04/17</t>
   </si>
 </sst>
 </file>
@@ -712,7 +715,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>585000</v>
+        <v>697000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1685,17 +1688,23 @@
     <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <f t="shared" si="2"/>
-        <v>585000</v>
-      </c>
-      <c r="B66" s="6"/>
+        <v>697000</v>
+      </c>
+      <c r="B66" s="6">
+        <v>112000</v>
+      </c>
       <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="3"/>
+      <c r="D66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>585000</v>
+        <v>697000</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -1705,7 +1714,7 @@
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>585000</v>
+        <v>697000</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -1715,7 +1724,7 @@
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <f t="shared" si="2"/>
-        <v>585000</v>
+        <v>697000</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -1725,7 +1734,7 @@
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>585000</v>
+        <v>697000</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1736,7 +1745,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="7">
         <f>SUM(B52:B70)+B46</f>
-        <v>4503000</v>
+        <v>4615000</v>
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
@@ -1748,7 +1757,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>585000</v>
+        <v>697000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -253,6 +253,15 @@
   </si>
   <si>
     <t>1405/04/17</t>
+  </si>
+  <si>
+    <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>کیک رضا</t>
+  </si>
+  <si>
+    <t>ساندویچ باغ ممد جواد</t>
   </si>
 </sst>
 </file>
@@ -715,7 +724,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>697000</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1704,37 +1713,51 @@
     <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <f t="shared" si="2"/>
-        <v>697000</v>
-      </c>
-      <c r="B67" s="6"/>
+        <v>799000</v>
+      </c>
+      <c r="B67" s="6">
+        <v>102000</v>
+      </c>
       <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="3"/>
+      <c r="D67" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <f t="shared" si="2"/>
-        <v>697000</v>
-      </c>
-      <c r="B68" s="6"/>
+        <v>884000</v>
+      </c>
+      <c r="B68" s="6">
+        <v>85000</v>
+      </c>
       <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
+      <c r="D68" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <f t="shared" si="2"/>
-        <v>697000</v>
-      </c>
-      <c r="B69" s="6"/>
+        <v>1030000</v>
+      </c>
+      <c r="B69" s="6">
+        <v>146000</v>
+      </c>
       <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="D69" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>697000</v>
+        <v>1030000</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -1745,7 +1768,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="7">
         <f>SUM(B52:B70)+B46</f>
-        <v>4615000</v>
+        <v>4948000</v>
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
@@ -1757,7 +1780,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>697000</v>
+        <v>1030000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>ساندویچ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>گوب</t>
   </si>
 </sst>
 </file>
@@ -724,7 +730,7 @@
       </c>
       <c r="H2" s="9">
         <f>A72</f>
-        <v>1030000</v>
+        <v>1192000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1757,18 +1763,24 @@
     <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <f t="shared" si="2"/>
-        <v>1030000</v>
-      </c>
-      <c r="B70" s="6"/>
+        <v>1192000</v>
+      </c>
+      <c r="B70" s="6">
+        <v>162000</v>
+      </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="3"/>
+      <c r="D70" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
       <c r="B71" s="7">
         <f>SUM(B52:B70)+B46</f>
-        <v>4948000</v>
+        <v>5110000</v>
       </c>
       <c r="C71" s="7">
         <f>SUM(C52:C70)+C46</f>
@@ -1780,7 +1792,7 @@
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="11">
         <f>A70</f>
-        <v>1030000</v>
+        <v>1192000</v>
       </c>
       <c r="B72" s="11"/>
       <c r="C72" s="10" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>گوب</t>
+  </si>
+  <si>
+    <t>1405/05/09</t>
   </si>
 </sst>
 </file>
@@ -375,7 +378,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -729,8 +746,8 @@
         <v>1</v>
       </c>
       <c r="H2" s="9">
-        <f>A72</f>
-        <v>1192000</v>
+        <f>A97</f>
+        <v>1354000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1813,44 +1830,277 @@
       <c r="E73" s="4"/>
     </row>
     <row r="74" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="6">
+        <f>B77-C77+A72</f>
+        <v>1354000</v>
+      </c>
+      <c r="B77" s="6">
+        <v>162000</v>
+      </c>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="6">
+        <f>A77+B78-C78</f>
+        <v>1354000</v>
+      </c>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="6">
+        <f t="shared" ref="A79:A95" si="3">A78+B79-C79</f>
+        <v>1354000</v>
+      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="6">
+        <f t="shared" si="3"/>
+        <v>1354000</v>
+      </c>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="7"/>
+      <c r="B96" s="7">
+        <f>SUM(B77:B95)+B71</f>
+        <v>5272000</v>
+      </c>
+      <c r="C96" s="7">
+        <f>SUM(C77:C95)+C71</f>
+        <v>3918000</v>
+      </c>
+      <c r="D96" s="7"/>
+      <c r="E96" s="5"/>
+    </row>
+    <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="11">
+        <f>A95</f>
+        <v>1354000</v>
+      </c>
+      <c r="B97" s="11"/>
+      <c r="C97" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="10"/>
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="113" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1866,7 +2116,9 @@
     <row r="125" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="126" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A47:B47"/>
@@ -1875,14 +2127,22 @@
     <mergeCell ref="C72:D72"/>
   </mergeCells>
   <conditionalFormatting sqref="A23:B23">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:B47">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72:B72">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -1890,7 +2150,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72:B72">
+  <conditionalFormatting sqref="A97:B97">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>1405/05/09</t>
+  </si>
+  <si>
+    <t>1405/05/11</t>
   </si>
 </sst>
 </file>
@@ -368,10 +371,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -747,7 +750,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1086,15 +1089,15 @@
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <f>A21</f>
         <v>555000</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="10"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
@@ -1447,15 +1450,15 @@
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11">
+      <c r="A47" s="10">
         <f>A45</f>
         <v>653000</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="10" t="s">
+      <c r="B47" s="10"/>
+      <c r="C47" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="10"/>
+      <c r="D47" s="11"/>
       <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1807,15 +1810,15 @@
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="11">
+      <c r="A72" s="10">
         <f>A70</f>
         <v>1192000</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="10"/>
+      <c r="C72" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D72" s="10"/>
+      <c r="D72" s="11"/>
       <c r="E72" s="4"/>
     </row>
     <row r="73" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1874,17 +1877,23 @@
     <row r="78" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <f>A77+B78-C78</f>
-        <v>1354000</v>
-      </c>
-      <c r="B78" s="6"/>
+        <v>1894000</v>
+      </c>
+      <c r="B78" s="6">
+        <v>540000</v>
+      </c>
       <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="3"/>
+      <c r="D78" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <f t="shared" ref="A79:A95" si="3">A78+B79-C79</f>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -1894,7 +1903,7 @@
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -1904,7 +1913,7 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1914,7 +1923,7 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1924,7 +1933,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1934,7 +1943,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1944,7 +1953,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1954,7 +1963,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1964,7 +1973,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1974,7 +1983,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -1984,7 +1993,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -1994,7 +2003,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2004,7 +2013,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2014,7 +2023,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2024,7 +2033,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2034,7 +2043,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2044,7 +2053,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>1354000</v>
+        <v>1894000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2055,7 +2064,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>5272000</v>
+        <v>5812000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2065,15 +2074,15 @@
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="11">
+      <c r="A97" s="10">
         <f>A95</f>
-        <v>1354000</v>
-      </c>
-      <c r="B97" s="11"/>
-      <c r="C97" s="10" t="s">
+        <v>1894000</v>
+      </c>
+      <c r="B97" s="10"/>
+      <c r="C97" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D97" s="10"/>
+      <c r="D97" s="11"/>
       <c r="E97" s="4"/>
     </row>
     <row r="98" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>1405/05/11</t>
+  </si>
+  <si>
+    <t>1405/05/13</t>
+  </si>
+  <si>
+    <t>گول بازی مزه باغ دامو</t>
   </si>
 </sst>
 </file>
@@ -750,7 +756,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1893,17 +1899,23 @@
     <row r="79" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <f t="shared" ref="A79:A95" si="3">A78+B79-C79</f>
-        <v>1894000</v>
-      </c>
-      <c r="B79" s="6"/>
+        <v>2153000</v>
+      </c>
+      <c r="B79" s="6">
+        <v>259000</v>
+      </c>
       <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="3"/>
+      <c r="D79" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -1913,7 +1925,7 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1923,7 +1935,7 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1933,7 +1945,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1943,7 +1955,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1953,7 +1965,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1963,7 +1975,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1973,7 +1985,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1983,7 +1995,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -1993,7 +2005,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2003,7 +2015,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2013,7 +2025,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2023,7 +2035,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2033,7 +2045,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2043,7 +2055,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2053,7 +2065,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2064,7 +2076,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>5812000</v>
+        <v>6071000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2076,7 +2088,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>1894000</v>
+        <v>2153000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>گول بازی مزه باغ دامو</t>
+  </si>
+  <si>
+    <t>1405/05/23</t>
   </si>
 </sst>
 </file>
@@ -756,7 +759,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1915,17 +1918,23 @@
     <row r="80" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
-      </c>
-      <c r="B80" s="6"/>
+        <v>2315000</v>
+      </c>
+      <c r="B80" s="6">
+        <v>162000</v>
+      </c>
       <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="3"/>
+      <c r="D80" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -1935,7 +1944,7 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1945,7 +1954,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1955,7 +1964,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1965,7 +1974,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1975,7 +1984,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1985,7 +1994,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -1995,7 +2004,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2005,7 +2014,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2015,7 +2024,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2025,7 +2034,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2035,7 +2044,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2045,7 +2054,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2055,7 +2064,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2065,7 +2074,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2076,7 +2085,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6071000</v>
+        <v>6233000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2088,7 +2097,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2153000</v>
+        <v>2315000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -282,7 +282,7 @@
     <t>گول بازی مزه باغ دامو</t>
   </si>
   <si>
-    <t>1405/05/23</t>
+    <t>1405/05/26</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,9 +1934,11 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
-      </c>
-      <c r="B81" s="6"/>
+        <v>2315500</v>
+      </c>
+      <c r="B81" s="6">
+        <v>500</v>
+      </c>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="3"/>
@@ -1944,7 +1946,7 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1954,7 +1956,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1964,7 +1966,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1974,7 +1976,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1984,7 +1986,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1994,7 +1996,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2004,7 +2006,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2014,7 +2016,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2024,7 +2026,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2034,7 +2036,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2044,7 +2046,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2054,7 +2056,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2064,7 +2066,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2074,7 +2076,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2085,7 +2087,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6233000</v>
+        <v>6233500</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2097,7 +2099,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2315000</v>
+        <v>2315500</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,11 +1934,9 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
-      </c>
-      <c r="B81" s="6">
-        <v>500</v>
-      </c>
+        <v>2315000</v>
+      </c>
+      <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
       <c r="E81" s="3"/>
@@ -1946,7 +1944,7 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1956,7 +1954,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1966,7 +1964,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1976,7 +1974,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1986,7 +1984,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1996,7 +1994,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2006,7 +2004,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2016,7 +2014,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2026,7 +2024,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2036,7 +2034,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2046,7 +2044,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2056,7 +2054,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2066,7 +2064,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2076,7 +2074,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2087,7 +2085,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6233500</v>
+        <v>6233000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2099,7 +2097,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2315500</v>
+        <v>2315000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="90">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>مزه</t>
   </si>
 </sst>
 </file>
@@ -723,6 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -759,7 +766,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,17 +1941,23 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
-      </c>
-      <c r="B81" s="6"/>
+        <v>2386000</v>
+      </c>
+      <c r="B81" s="6">
+        <v>71000</v>
+      </c>
       <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="3"/>
+      <c r="D81" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -1954,7 +1967,7 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1964,7 +1977,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1974,7 +1987,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1984,7 +1997,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1994,7 +2007,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2004,7 +2017,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2014,7 +2027,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2024,7 +2037,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2034,7 +2047,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2044,7 +2057,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2054,7 +2067,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2064,7 +2077,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2074,7 +2087,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2085,7 +2098,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6233000</v>
+        <v>6304000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2097,7 +2110,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2315000</v>
+        <v>2386000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>مزه</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -766,7 +769,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1957,17 +1960,23 @@
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
-      </c>
-      <c r="B82" s="6"/>
+        <v>2575000</v>
+      </c>
+      <c r="B82" s="6">
+        <v>189000</v>
+      </c>
       <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="3"/>
+      <c r="D82" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1977,7 +1986,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1987,7 +1996,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1997,7 +2006,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2007,7 +2016,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2017,7 +2026,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2027,7 +2036,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2037,7 +2046,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2047,7 +2056,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2057,7 +2066,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2067,7 +2076,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2077,7 +2086,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2087,7 +2096,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2098,7 +2107,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6304000</v>
+        <v>6493000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2110,7 +2119,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2386000</v>
+        <v>2575000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -292,6 +292,12 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/09</t>
+  </si>
+  <si>
+    <t>مزه پل دوآب</t>
   </si>
 </sst>
 </file>
@@ -769,7 +775,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1976,17 +1982,23 @@
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
-      </c>
-      <c r="B83" s="6"/>
+        <v>2745000</v>
+      </c>
+      <c r="B83" s="6">
+        <v>170000</v>
+      </c>
       <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="3"/>
+      <c r="D83" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1996,7 +2008,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2006,7 +2018,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2016,7 +2028,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2026,7 +2038,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2036,7 +2048,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2046,7 +2058,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2056,7 +2068,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2066,7 +2078,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2076,7 +2088,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2086,7 +2098,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2096,7 +2108,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2107,7 +2119,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6493000</v>
+        <v>6663000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2119,7 +2131,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2575000</v>
+        <v>2745000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
   </si>
 </sst>
 </file>
@@ -775,7 +778,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1998,17 +2001,23 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
-      </c>
-      <c r="B84" s="6"/>
+        <v>2900000</v>
+      </c>
+      <c r="B84" s="6">
+        <v>155000</v>
+      </c>
       <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="3"/>
+      <c r="D84" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -2018,7 +2027,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2028,7 +2037,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2038,7 +2047,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2048,7 +2057,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2058,7 +2067,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2068,7 +2077,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2078,7 +2087,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2088,7 +2097,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2098,7 +2107,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2108,7 +2117,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2119,7 +2128,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6663000</v>
+        <v>6818000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2131,7 +2140,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2745000</v>
+        <v>2900000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -778,7 +781,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2017,17 +2020,23 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
-      </c>
-      <c r="B85" s="6"/>
+        <v>3087000</v>
+      </c>
+      <c r="B85" s="6">
+        <v>187000</v>
+      </c>
       <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="3"/>
+      <c r="D85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -2037,7 +2046,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2047,7 +2056,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2057,7 +2066,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2067,7 +2076,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2077,7 +2086,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2087,7 +2096,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2097,7 +2106,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2107,7 +2116,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2117,7 +2126,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2128,7 +2137,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6818000</v>
+        <v>7005000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2140,7 +2149,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2900000</v>
+        <v>3087000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>1405/06/18</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -781,7 +790,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2036,27 +2045,37 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
-      </c>
-      <c r="B86" s="6"/>
+        <v>3183000</v>
+      </c>
+      <c r="B86" s="6">
+        <v>96000</v>
+      </c>
       <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="3"/>
+      <c r="D86" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
-      </c>
-      <c r="B87" s="6"/>
+        <v>3413000</v>
+      </c>
+      <c r="B87" s="6">
+        <v>230000</v>
+      </c>
       <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
+      <c r="D87" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2066,7 +2085,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2076,7 +2095,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2086,7 +2105,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2096,7 +2115,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2106,7 +2125,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2116,7 +2135,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2126,7 +2145,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2137,7 +2156,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7005000</v>
+        <v>7331000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2149,7 +2168,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3087000</v>
+        <v>3413000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">
